--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DEE969F-BA3C-4785-BF6C-6AB7523B5534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CD3374-0452-45F3-9BB5-B45BE41BD8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44880" yWindow="13680" windowWidth="29040" windowHeight="15720" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
+    <workbookView xWindow="4908" yWindow="12864" windowWidth="18192" windowHeight="11472" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>tc={B9F7BAD0-07CE-487B-A322-95E12025CAA4}</author>
   </authors>
   <commentList>
-    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="131">
   <si>
     <t>ICON 2021</t>
   </si>
@@ -437,6 +437,48 @@
   </si>
   <si>
     <t>publications/presentations/model1_derivation.pdf</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>An</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Introduction to Reasoning Models</t>
+    </r>
+  </si>
+  <si>
+    <t>Building  NLP Datasets at scale for Indian languages</t>
+  </si>
+  <si>
+    <t>Empowering India Through Inclusive Generative AI , IIT Bhubaneshwar (upcoming)</t>
+  </si>
+  <si>
+    <t>IASNLP, IIIT Hyderabad (upcoming)</t>
   </si>
 </sst>
 </file>
@@ -497,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -529,7 +571,16 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -872,7 +923,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E33" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+  <threadedComment ref="E35" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
     <text xml:space="preserve">PPT lost
 </text>
   </threadedComment>
@@ -881,15 +932,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACF2BB-E7E8-434C-99B1-90D8952D6521}">
-  <dimension ref="A1:G41"/>
-  <sheetFormatPr defaultColWidth="29.3671875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr defaultColWidth="29.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="29.3671875" style="1"/>
-    <col min="3" max="3" width="29.3671875" style="9"/>
-    <col min="4" max="16384" width="29.3671875" style="1"/>
+    <col min="1" max="2" width="29.36328125" style="1"/>
+    <col min="3" max="3" width="29.36328125" style="9"/>
+    <col min="4" max="16384" width="29.36328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -912,177 +963,178 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="9">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="14">
         <v>2025</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>120</v>
+        <v>128</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>123</v>
+        <v>87</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="E4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2025</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C7" s="9">
         <v>2024</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C8" s="9">
         <v>2024</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="9">
-        <v>2023</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="9">
-        <v>2023</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2023</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="9">
+        <v>2023</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C9" s="9">
-        <v>2022</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <v>2022</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="11">
         <v>2022</v>
@@ -1091,522 +1143,550 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="C13" s="11">
         <v>2022</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="G13" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="9">
-        <v>2021</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="9">
-        <v>2021</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C16" s="9">
         <v>2021</v>
       </c>
+      <c r="D16" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E16" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="C17" s="9">
         <v>2021</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="11">
+        <v>109</v>
+      </c>
+      <c r="C18" s="9">
         <v>2021</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="G18" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="C19" s="9">
         <v>2021</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="9">
+        <v>112</v>
+      </c>
+      <c r="C20" s="11">
         <v>2021</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="E20" s="7"/>
       <c r="G20" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="C21" s="9">
         <v>2021</v>
       </c>
+      <c r="E21" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="G21" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="11">
-        <v>2020</v>
+        <v>57</v>
+      </c>
+      <c r="C22" s="9">
+        <v>2021</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>52</v>
+        <v>101</v>
+      </c>
+      <c r="C23" s="9">
+        <v>2021</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C24" s="11">
         <v>2020</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="C25" s="11">
         <v>2020</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C26" s="11">
         <v>2020</v>
       </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="1" t="s">
+    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C29" s="11">
         <v>2019</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="G27" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="E29" s="7"/>
       <c r="G29" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C30" s="10">
-        <v>2018</v>
+        <v>105</v>
+      </c>
+      <c r="C30" s="11">
+        <v>2019</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="C31" s="9">
         <v>2018</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" s="9">
+        <v>100</v>
+      </c>
+      <c r="C32" s="10">
         <v>2018</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C33" s="9">
         <v>2018</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C34" s="9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="9">
+        <v>2018</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G35" s="1" t="s">
+      <c r="B36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="9">
+        <v>2017</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C37" s="9">
-        <v>2015</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>74</v>
+        <v>2016</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C38" s="9">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C39" s="9">
+        <v>2015</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="9">
+        <v>2015</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C41" s="9">
         <v>2013</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="1" t="s">
+    <row r="42" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B42" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C42" s="9">
         <v>2012</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="1" t="s">
+    <row r="43" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B43" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C43" s="9">
         <v>2012</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G41">
-    <sortCondition descending="1" ref="C2:C41"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G43">
+    <sortCondition descending="1" ref="C4:C43"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3CD3374-0452-45F3-9BB5-B45BE41BD8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A7CDD6-D6C6-4AA3-AB6A-A9A0A68156D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4908" yWindow="12864" windowWidth="18192" windowHeight="11472" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
+    <workbookView xWindow="-96" yWindow="12864" windowWidth="18192" windowHeight="11472" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="132">
   <si>
     <t>ICON 2021</t>
   </si>
@@ -472,13 +472,16 @@
     </r>
   </si>
   <si>
-    <t>Building  NLP Datasets at scale for Indian languages</t>
-  </si>
-  <si>
     <t>Empowering India Through Inclusive Generative AI , IIT Bhubaneshwar (upcoming)</t>
   </si>
   <si>
-    <t>IASNLP, IIIT Hyderabad (upcoming)</t>
+    <t>Building Multilingual NLP datasets at scale</t>
+  </si>
+  <si>
+    <t>IASNLP, IIIT-Hyderabad</t>
+  </si>
+  <si>
+    <t>publications/presentations/iasnlp_iiith_building_datasets_2025.pdf</t>
   </si>
 </sst>
 </file>
@@ -539,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -574,14 +577,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -933,14 +930,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACF2BB-E7E8-434C-99B1-90D8952D6521}">
   <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="29.36328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="29.3671875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="2" width="29.36328125" style="1"/>
-    <col min="3" max="3" width="29.36328125" style="9"/>
-    <col min="4" max="16384" width="29.36328125" style="1"/>
+    <col min="1" max="2" width="29.3671875" style="1"/>
+    <col min="3" max="3" width="29.3671875" style="9"/>
+    <col min="4" max="16384" width="29.3671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -963,14 +960,14 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="14">
+      <c r="B2" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="9">
         <v>2025</v>
       </c>
       <c r="D2" s="2"/>
@@ -978,9 +975,9 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>130</v>
@@ -988,11 +985,14 @@
       <c r="C3" s="9">
         <v>2025</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>131</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>87</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>119</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -1064,7 +1064,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>118</v>
       </c>
@@ -1098,7 +1098,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
@@ -1115,7 +1115,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>63</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>110</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>108</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>49</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>111</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1291,7 +1291,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>63</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>51</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>10</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1376,7 +1376,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>12</v>
       </c>
@@ -1416,7 +1416,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -1431,7 +1431,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>22</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>104</v>
       </c>
@@ -1499,7 +1499,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>18</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>8</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>24</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>24</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>6</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -1627,7 +1627,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>27</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>26</v>
       </c>

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81A7CDD6-D6C6-4AA3-AB6A-A9A0A68156D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274BA493-4B3B-41E6-8FD8-B93F8D5A771D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="12864" windowWidth="18192" windowHeight="11472" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>tc={B9F7BAD0-07CE-487B-A322-95E12025CAA4}</author>
   </authors>
   <commentList>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+    <comment ref="E37" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="142">
   <si>
     <t>ICON 2021</t>
   </si>
@@ -322,9 +322,6 @@
   </si>
   <si>
     <t>Raj Dabre, Rudramurthy V, Mohammed Safi Ur Rahman, Thanmay Jayakumar</t>
-  </si>
-  <si>
-    <t>https://github.com/anoopkunchukuttan/multilingual_extend_llm</t>
   </si>
   <si>
     <t>ICON, Thiruvanthapuram, India</t>
@@ -422,9 +419,6 @@
   </si>
   <si>
     <t>publications/presentations/DeepSeek-OSSProjects-Intro-Feb2025.pdf</t>
-  </si>
-  <si>
-    <t>EMNLP, Suzhou, China (upcoming)</t>
   </si>
   <si>
     <t>IIT Guwahati Winter School on Deep Learning for Vision and Language Modelling, Guwahati, India</t>
@@ -472,9 +466,6 @@
     </r>
   </si>
   <si>
-    <t>Empowering India Through Inclusive Generative AI , IIT Bhubaneshwar (upcoming)</t>
-  </si>
-  <si>
     <t>Building Multilingual NLP datasets at scale</t>
   </si>
   <si>
@@ -482,13 +473,52 @@
   </si>
   <si>
     <t>publications/presentations/iasnlp_iiith_building_datasets_2025.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMNLP, Suzhou, China </t>
+  </si>
+  <si>
+    <t>https://us06web.zoom.us/rec/play/lIFALsa8z5K4Zi38sk5-rqsU9ACypYIniZAxbFhgU0SiRftBzLinKQP9YZhYiTLq6kFui7B5vAPgQwhS.DA_YFrA1N9-76ng1?eagerLoadZvaPages=sidemenu.billing.plan_management&amp;isReferralProgramEnabled=false&amp;isReferralProgramAvailable=false&amp;accessLevel=meeting&amp;canPlayFromShare=true&amp;from=share_recording_detail&amp;startTime=1762579923000&amp;componentName=rec-play&amp;originRequestUrl=https%3A%2F%2Fus06web.zoom.us%2Frec%2Fshare%2FFnJVUbXJUa4dONJ9ZyVnNi45faGksKxW18j6C5pHSncdXJwIY3A93g9lDc3Mbcgq.yfl7n9q8E_k18TZN%3FstartTime%3D1762579923000</t>
+  </si>
+  <si>
+    <t>https://ai4bharat.github.io/multilingual-llm-expand-emnlp-2025/multilingual-llm-expand-emnlp-2025-slides.pdf</t>
+  </si>
+  <si>
+    <t>Language Technology in AI and NLP: Indian Languages in the Digital Age</t>
+  </si>
+  <si>
+    <t>Bharatiya Bhasa Sangam, EFLU Hyderabad</t>
+  </si>
+  <si>
+    <t>publications/presentations/eflu_talk_ai_indicnlp_2025.pdf</t>
+  </si>
+  <si>
+    <t>publications/presentations/OdiaGen_ReasoningModelsIntro_2025.pdf</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=WQtRrp01d04</t>
+  </si>
+  <si>
+    <t>Empowering India Through Inclusive Generative AI , IIT Bhubaneshwar</t>
+  </si>
+  <si>
+    <t>https://www.cse.iitb.ac.in/~cs772</t>
+  </si>
+  <si>
+    <t>Guest Lectures for CS-772 (Deep Learning for NLP) by Prof. Pushpak Bhattacharyya, Dept of Computer Science, IIT Bombay [Lectures 9 and 12]</t>
+  </si>
+  <si>
+    <t>Lectures as part of CS-772 (Deep Learning for NLP) course by Prof. Pushpak Bhattacharyya at Dept of Computer Science, IIT Bombay  [Lectures 9 and 11]</t>
+  </si>
+  <si>
+    <t>https://www.cfilt.iitb.ac.in/~cs772-2022/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -511,6 +541,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -539,10 +577,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -580,8 +619,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -920,7 +978,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E35" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+  <threadedComment ref="E37" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
     <text xml:space="preserve">PPT lost
 </text>
   </threadedComment>
@@ -929,15 +987,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACF2BB-E7E8-434C-99B1-90D8952D6521}">
-  <dimension ref="A1:G43"/>
-  <sheetFormatPr defaultColWidth="29.3671875" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="29.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="29.3671875" style="1"/>
-    <col min="3" max="3" width="29.3671875" style="9"/>
-    <col min="4" max="16384" width="29.3671875" style="1"/>
+    <col min="1" max="2" width="29.33203125" style="1"/>
+    <col min="3" max="3" width="29.33203125" style="9"/>
+    <col min="4" max="16384" width="29.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -960,206 +1018,226 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C2" s="9">
+    <row r="2" spans="1:7" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="15">
         <v>2025</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="E2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="4" customFormat="1" ht="288" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
       </c>
+      <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="E3" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="1" t="s">
-        <v>87</v>
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>88</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="9">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="10">
         <v>2025</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="D5" s="16"/>
+      <c r="E5" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="9">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C9" s="9">
         <v>2024</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="1" t="s">
+    <row r="10" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="9">
-        <v>2024</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2023</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>102</v>
       </c>
       <c r="C10" s="9">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>67</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2023</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="9">
+        <v>2023</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="9">
+      <c r="B13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="10">
         <v>2022</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="E13" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="1" t="s">
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>116</v>
@@ -1171,531 +1249,562 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="C15" s="11">
         <v>2022</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="G15" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="11">
+        <v>2022</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="9">
-        <v>2021</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="9">
-        <v>2021</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="C18" s="9">
         <v>2021</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E18" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="C19" s="9">
         <v>2021</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C20" s="11">
+        <v>108</v>
+      </c>
+      <c r="C20" s="9">
         <v>2021</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="G20" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="C21" s="9">
         <v>2021</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="9">
+        <v>111</v>
+      </c>
+      <c r="C22" s="11">
         <v>2021</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="E22" s="7"/>
       <c r="G22" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="C23" s="9">
         <v>2021</v>
       </c>
+      <c r="E23" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="G23" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C24" s="11">
-        <v>2020</v>
+        <v>57</v>
+      </c>
+      <c r="C24" s="9">
+        <v>2021</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="C25" s="9">
+        <v>2021</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C26" s="11">
         <v>2020</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="C27" s="11">
         <v>2020</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C28" s="11">
         <v>2020</v>
       </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="1" t="s">
+    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C31" s="11">
         <v>2019</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="G29" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>68</v>
-      </c>
+      <c r="E31" s="7"/>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="10">
-        <v>2018</v>
+        <v>104</v>
+      </c>
+      <c r="C32" s="11">
+        <v>2019</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="C33" s="9">
         <v>2018</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="9">
+        <v>99</v>
+      </c>
+      <c r="C34" s="10">
         <v>2018</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C35" s="9">
         <v>2018</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="9">
+        <v>2018</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C37" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="1" t="s">
+      <c r="C38" s="9">
+        <v>2017</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="9">
-        <v>2015</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>74</v>
+        <v>2016</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C40" s="9">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="9">
+        <v>2015</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C42" s="9">
+        <v>2015</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="9">
+        <v>2013</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C41" s="9">
-        <v>2013</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C42" s="9">
+      <c r="C44" s="9">
         <v>2012</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="72" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="1" t="s">
+    <row r="45" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C43" s="9">
+      <c r="B45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" s="9">
         <v>2012</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="G43" s="1" t="s">
+      <c r="E45" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:G43">
-    <sortCondition descending="1" ref="C4:C43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:G45">
+    <sortCondition descending="1" ref="C7:C45"/>
   </sortState>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{f42aa342-8706-4288-bd11-ebb85995028c}" enabled="1" method="Standard" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
+  <clbl:label id="{87ba5c36-b7cf-4793-bbc2-bd5b3a9f95ca}" enabled="1" method="Privileged" siteId="{72f988bf-86f1-41af-91ab-2d7cd011db47}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>
--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274BA493-4B3B-41E6-8FD8-B93F8D5A771D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A54793D-37C0-49DD-A3B2-8CDC3B950278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
@@ -41,7 +41,7 @@
     <author>tc={B9F7BAD0-07CE-487B-A322-95E12025CAA4}</author>
   </authors>
   <commentList>
-    <comment ref="E37" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
   <si>
     <t>ICON 2021</t>
   </si>
@@ -513,12 +513,55 @@
   <si>
     <t>https://www.cfilt.iitb.ac.in/~cs772-2022/</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trustworthy AI for Social Good: From Multimodal Learning to Large Language Models, NIT Surathkal, Pre-Summit Events for AI Impact Summit 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(upcoming)</t>
+    </r>
+  </si>
+  <si>
+    <t>Panel Discussion</t>
+  </si>
+  <si>
+    <t>Language Resources for AI in Indian Languages</t>
+  </si>
+  <si>
+    <t>CIIL</t>
+  </si>
+  <si>
+    <t>Workshop on Machine Translation</t>
+  </si>
+  <si>
+    <t>NLP/MT for low-resource languages </t>
+  </si>
+  <si>
+    <t>AI Days Conference, Hyderabad, India</t>
+  </si>
+  <si>
+    <t>Indian language NLP and LLMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI's Impact: A Balancing Act </t>
+  </si>
+  <si>
+    <t>Wikimedia Technology Summit</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -549,6 +592,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -619,15 +670,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -636,6 +678,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -978,7 +1029,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E37" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+  <threadedComment ref="E42" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
     <text xml:space="preserve">PPT lost
 </text>
   </threadedComment>
@@ -987,15 +1038,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACF2BB-E7E8-434C-99B1-90D8952D6521}">
-  <dimension ref="A1:G45"/>
-  <sheetFormatPr defaultColWidth="29.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultColWidth="29.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="29.33203125" style="1"/>
-    <col min="3" max="3" width="29.33203125" style="9"/>
-    <col min="4" max="16384" width="29.33203125" style="1"/>
+    <col min="1" max="2" width="29.28515625" style="1"/>
+    <col min="3" max="3" width="29.28515625" style="9"/>
+    <col min="4" max="16384" width="29.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -1018,784 +1069,869 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="14" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="18">
+        <v>2025</v>
+      </c>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B4" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="C2" s="15">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="4" customFormat="1" ht="288" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="9">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
       </c>
-      <c r="D4" s="2"/>
       <c r="E4" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="18" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="10">
+    <row r="5" spans="1:7" s="4" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="9">
         <v>2025</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>136</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>127</v>
+      <c r="D5" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
       </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" s="9">
+        <v>135</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="10">
         <v>2025</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="D7" s="13"/>
+      <c r="E7" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C10" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="18">
+        <v>2024</v>
+      </c>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C12" s="9">
         <v>2024</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="13" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C13" s="9">
         <v>2024</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C14" s="9">
         <v>2023</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C15" s="9">
         <v>2023</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="7" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
+    <row r="16" spans="1:7" s="7" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B16" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C16" s="10">
         <v>2022</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E16" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G16" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="C17" s="11">
         <v>2022</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="G17" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11">
+        <v>2022</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="C18" s="9">
-        <v>2021</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="9">
-        <v>2021</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="9">
-        <v>2021</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="C21" s="9">
         <v>2021</v>
       </c>
+      <c r="D21" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E21" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="11">
+    <row r="22" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" s="18">
         <v>2021</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="G22" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C23" s="9">
         <v>2021</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C24" s="9">
         <v>2021</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C25" s="9">
         <v>2021</v>
       </c>
+      <c r="E25" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="G25" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="11">
+        <v>2021</v>
+      </c>
+      <c r="E26" s="7"/>
+      <c r="G26" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="9">
+        <v>2021</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="9">
+        <v>2021</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="29" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="9">
+        <v>2021</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C26" s="11">
-        <v>2020</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="11">
-        <v>2020</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="C30" s="11">
         <v>2020</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G30" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C31" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E31" s="7"/>
+        <v>2020</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="G31" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>104</v>
+        <v>3</v>
       </c>
       <c r="C32" s="11">
-        <v>2019</v>
+        <v>2020</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="9">
-        <v>2018</v>
+        <v>105</v>
+      </c>
+      <c r="C33" s="11">
+        <v>2020</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="18">
+        <v>2020</v>
+      </c>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="11">
+        <v>2019</v>
+      </c>
+      <c r="E36" s="7"/>
+      <c r="G36" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" s="10">
-        <v>2018</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="9">
-        <v>2018</v>
+        <v>104</v>
+      </c>
+      <c r="C37" s="11">
+        <v>2019</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="C38" s="9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>25</v>
+        <v>99</v>
+      </c>
+      <c r="C39" s="10">
+        <v>2018</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C40" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>7</v>
+        <v>2018</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C41" s="9">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C42" s="9">
-        <v>2015</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>20</v>
+        <v>2018</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C43" s="9">
-        <v>2013</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>15</v>
+        <v>2017</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>91</v>
+        <v>24</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="C44" s="9">
-        <v>2012</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>77</v>
+        <v>2016</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="9">
+        <v>2016</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="9">
+        <v>2015</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="9">
+        <v>2015</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="9">
+        <v>2013</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49" s="9">
+        <v>2012</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B50" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C50" s="9">
         <v>2012</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:G45">
-    <sortCondition descending="1" ref="C7:C45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G50">
+    <sortCondition descending="1" ref="C9:C50"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
+    <hyperlink ref="E7" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A54793D-37C0-49DD-A3B2-8CDC3B950278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825E8284-E274-4567-BD55-5F994CD3E2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
@@ -542,9 +542,6 @@
     <t>Workshop on Machine Translation</t>
   </si>
   <si>
-    <t>NLP/MT for low-resource languages </t>
-  </si>
-  <si>
     <t>AI Days Conference, Hyderabad, India</t>
   </si>
   <si>
@@ -555,6 +552,9 @@
   </si>
   <si>
     <t>Wikimedia Technology Summit</t>
+  </si>
+  <si>
+    <t>NLP/MT for low-resource languages</t>
   </si>
 </sst>
 </file>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="2" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C2" s="18">
         <v>2025</v>
@@ -1237,10 +1237,10 @@
     </row>
     <row r="11" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>150</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>151</v>
       </c>
       <c r="C11" s="18">
         <v>2024</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="34" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>146</v>

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825E8284-E274-4567-BD55-5F994CD3E2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4072B2-1E38-459C-84F1-1120227A2C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>tc={B9F7BAD0-07CE-487B-A322-95E12025CAA4}</author>
   </authors>
   <commentList>
-    <comment ref="E42" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="160">
   <si>
     <t>ICON 2021</t>
   </si>
@@ -555,6 +555,30 @@
   </si>
   <si>
     <t>NLP/MT for low-resource languages</t>
+  </si>
+  <si>
+    <t>Dr. Bhagwan Chowdhry, Areena Arora</t>
+  </si>
+  <si>
+    <t>Is the Artificial Intelligence boom a bubble?</t>
+  </si>
+  <si>
+    <t>The Hindu In-Focus Parley podcast</t>
+  </si>
+  <si>
+    <t>publications/presentations/prof_pushpak_memorial_lecture_indoml_2025.pdf</t>
+  </si>
+  <si>
+    <t>publications/presentations/ai_bubble_hindu_podcast_dec25.pdf</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/podcast/in-focus-parley-is-the-artificial-intelligence-boom-a-bubble/article70412059.ece</t>
+  </si>
+  <si>
+    <t>Prof. Pushpak Memorial Lecture, IndoML 2025, BITS Hyderabad</t>
+  </si>
+  <si>
+    <t>Prof. Pushpak Bhattacharya: The Guru and the Visionary Paving the Way for Indic NLP</t>
   </si>
 </sst>
 </file>
@@ -632,7 +656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -684,9 +708,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1029,7 +1050,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E42" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+  <threadedComment ref="E44" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
     <text xml:space="preserve">PPT lost
 </text>
   </threadedComment>
@@ -1038,7 +1059,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACF2BB-E7E8-434C-99B1-90D8952D6521}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultColWidth="29.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="29.28515625" style="1"/>
@@ -1069,308 +1090,322 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" s="18">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="9">
         <v>2025</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17" t="s">
+      <c r="D3" s="17" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="18">
-        <v>2026</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="1" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>134</v>
-      </c>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="4" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>87</v>
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>125</v>
+      <c r="A6" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
       </c>
-      <c r="D6" s="2"/>
       <c r="E6" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C7" s="10">
+    <row r="7" spans="1:7" s="4" customFormat="1" ht="315" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="9">
         <v>2025</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>127</v>
+      <c r="D7" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
       </c>
+      <c r="D8" s="2"/>
       <c r="E8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="9">
+        <v>135</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="10">
         <v>2025</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="D9" s="13"/>
+      <c r="E9" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>126</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C10" s="9">
         <v>2025</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="18">
-        <v>2024</v>
-      </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17" t="s">
-        <v>143</v>
+    <row r="11" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="9">
+        <v>2025</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="C12" s="9">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>102</v>
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="C13" s="9">
         <v>2024</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="9">
-        <v>2023</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="9">
-        <v>2023</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="7" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="9">
+        <v>2023</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2023</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="7" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B18" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C18" s="10">
         <v>2022</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E18" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G18" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C17" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C18" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C19" s="11">
         <v>2022</v>
@@ -1381,361 +1416,358 @@
     </row>
     <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>113</v>
       </c>
       <c r="C20" s="11">
         <v>2022</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="G20" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C21" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="11">
+        <v>2022</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="9">
-        <v>2021</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="C22" s="18">
-        <v>2021</v>
-      </c>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C23" s="9">
         <v>2021</v>
       </c>
+      <c r="D23" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>108</v>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="C24" s="9">
         <v>2021</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="C25" s="9">
         <v>2021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="11">
+        <v>108</v>
+      </c>
+      <c r="C26" s="9">
         <v>2021</v>
       </c>
-      <c r="E26" s="7"/>
+      <c r="E26" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="G26" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="C27" s="9">
         <v>2021</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="9">
+        <v>111</v>
+      </c>
+      <c r="C28" s="11">
         <v>2021</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="E28" s="7"/>
       <c r="G28" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="C29" s="9">
         <v>2021</v>
       </c>
+      <c r="E29" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="G29" s="1" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="11">
-        <v>2020</v>
+        <v>57</v>
+      </c>
+      <c r="C30" s="9">
+        <v>2021</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="C31" s="9">
+        <v>2021</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="C32" s="11">
         <v>2020</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>105</v>
+        <v>11</v>
       </c>
       <c r="C33" s="11">
         <v>2020</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="16" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="C34" s="18">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="11">
         <v>2020</v>
       </c>
-      <c r="D34" s="17"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="D34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
       <c r="C35" s="11">
         <v>2020</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C36" s="9">
+        <v>2020</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E36" s="7"/>
-      <c r="G36" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C37" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>68</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C38" s="11">
+        <v>2019</v>
+      </c>
+      <c r="E38" s="7"/>
       <c r="G38" s="1" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="10">
-        <v>2018</v>
+        <v>104</v>
+      </c>
+      <c r="C39" s="11">
+        <v>2019</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="C40" s="9">
         <v>2018</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>85</v>
@@ -1743,195 +1775,226 @@
     </row>
     <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="9">
+        <v>99</v>
+      </c>
+      <c r="C41" s="10">
         <v>2018</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C42" s="9">
         <v>2018</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C43" s="9">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C44" s="9">
+        <v>2018</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C44" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G44" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="9">
+        <v>2017</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C46" s="9">
-        <v>2015</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>74</v>
+        <v>2016</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C47" s="9">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="9">
+        <v>2015</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="9">
+        <v>2015</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B50" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C50" s="9">
         <v>2013</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G50" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
+    <row r="51" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B51" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C51" s="9">
         <v>2012</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
+    <row r="52" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B52" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C52" s="9">
         <v>2012</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:G50">
-    <sortCondition descending="1" ref="C9:C50"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:G52">
+    <sortCondition descending="1" ref="C11:C52"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E7" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
+    <hyperlink ref="E9" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4072B2-1E38-459C-84F1-1120227A2C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACCD7CF-CE02-42C1-8926-279B0E75D139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
     <author>tc={B9F7BAD0-07CE-487B-A322-95E12025CAA4}</author>
   </authors>
   <commentList>
-    <comment ref="E44" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+    <comment ref="E45" authorId="0" shapeId="0" xr:uid="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
       <text>
         <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="165">
   <si>
     <t>ICON 2021</t>
   </si>
@@ -514,22 +514,6 @@
     <t>https://www.cfilt.iitb.ac.in/~cs772-2022/</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Trustworthy AI for Social Good: From Multimodal Learning to Large Language Models, NIT Surathkal, Pre-Summit Events for AI Impact Summit 2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(upcoming)</t>
-    </r>
-  </si>
-  <si>
     <t>Panel Discussion</t>
   </si>
   <si>
@@ -579,13 +563,31 @@
   </si>
   <si>
     <t>Prof. Pushpak Bhattacharya: The Guru and the Visionary Paving the Way for Indic NLP</t>
+  </si>
+  <si>
+    <t>U4nderstanding Trust and Safety in AI: From Code to Creativity</t>
+  </si>
+  <si>
+    <t>Roundtables at official pre-summit event ahead of the India AI Impact Summit 2026, IIIT-H, organized by SFLC.in, VISWAM.AI, FOSS United, and The Linux Foundation</t>
+  </si>
+  <si>
+    <t>images/sflc-roundtable-jan26.jpeg</t>
+  </si>
+  <si>
+    <t>AI4Bharat: Transforming the Landscape of Indian Language Technology</t>
+  </si>
+  <si>
+    <t>BITS Pilani, NLP Applications Course</t>
+  </si>
+  <si>
+    <t>publications/presentations/eai4bharat_bits_course_2026.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -616,14 +618,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1050,7 +1044,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E44" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
+  <threadedComment ref="E45" dT="2025-03-08T08:59:34.17" personId="{F1D8512E-E5B5-4DBB-941B-AF5E929619FB}" id="{B9F7BAD0-07CE-487B-A322-95E12025CAA4}">
     <text xml:space="preserve">PPT lost
 </text>
   </threadedComment>
@@ -1059,15 +1053,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBACF2BB-E7E8-434C-99B1-90D8952D6521}">
-  <dimension ref="A1:G52"/>
-  <sheetFormatPr defaultColWidth="29.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G53"/>
+  <sheetFormatPr defaultColWidth="29.26953125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="29.28515625" style="1"/>
-    <col min="3" max="3" width="29.28515625" style="9"/>
-    <col min="4" max="16384" width="29.28515625" style="1"/>
+    <col min="1" max="2" width="29.26953125" style="1"/>
+    <col min="3" max="3" width="29.26953125" style="9"/>
+    <col min="4" max="16384" width="29.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>78</v>
       </c>
@@ -1090,336 +1084,343 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>35</v>
+        <v>159</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C2" s="9">
         <v>2026</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="17" t="s">
+        <v>161</v>
+      </c>
       <c r="G2" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2026</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="9">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>158</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F4" s="2"/>
+      <c r="F4" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="G4" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="E5" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" ht="315" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>87</v>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>125</v>
+        <v>134</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="4" customFormat="1" ht="290" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="5" t="s">
+        <v>88</v>
+      </c>
       <c r="E8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2025</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="4" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="4" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="15" customFormat="1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+    <row r="10" spans="1:7" s="15" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B10" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C10" s="10">
         <v>2025</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F10" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="C10" s="9">
-        <v>2025</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
       </c>
-      <c r="D11" s="5"/>
       <c r="E11" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" s="4" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
       </c>
+      <c r="D12" s="5"/>
       <c r="E12" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="14" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C14" s="9">
         <v>2024</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>102</v>
+        <v>64</v>
       </c>
       <c r="C15" s="9">
         <v>2024</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="9">
+        <v>2024</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="9">
-        <v>2023</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>117</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C17" s="9">
         <v>2023</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="G17" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" s="7" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="9">
+        <v>2023</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="7" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B19" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C18" s="10">
+      <c r="C19" s="10">
         <v>2022</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E19" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G19" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="C19" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C20" s="11">
         <v>2022</v>
@@ -1428,12 +1429,12 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C21" s="11">
         <v>2022</v>
@@ -1442,536 +1443,533 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="C22" s="11">
         <v>2022</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="G22" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="11">
+        <v>2022</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="24" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B24" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="C23" s="9">
-        <v>2021</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="C24" s="9">
         <v>2021</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
+      <c r="D24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>47</v>
+      <c r="B25" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="C25" s="9">
         <v>2021</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C26" s="9">
         <v>2021</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C27" s="9">
         <v>2021</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="9">
+        <v>2021</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C29" s="11">
         <v>2021</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="G28" s="1" t="s">
+      <c r="E29" s="7"/>
+      <c r="G29" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="30" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C29" s="9">
-        <v>2021</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C30" s="9">
         <v>2021</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="C31" s="9">
         <v>2021</v>
       </c>
+      <c r="E31" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="G31" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="11">
-        <v>2020</v>
+        <v>100</v>
+      </c>
+      <c r="C32" s="9">
+        <v>2021</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="C33" s="11">
         <v>2020</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="G33" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C34" s="11">
         <v>2020</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>3</v>
       </c>
       <c r="C35" s="11">
         <v>2020</v>
       </c>
+      <c r="D35" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C36" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C36" s="9">
+    <row r="37" spans="1:7" s="3" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A37" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="9">
         <v>2020</v>
       </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C38" s="11">
         <v>2020</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F38" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C38" s="11">
-        <v>2019</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="G38" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>104</v>
       </c>
       <c r="C39" s="11">
         <v>2019</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="7"/>
+      <c r="G39" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="11">
+        <v>2019</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="41" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C41" s="9">
         <v>2018</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C42" s="10">
         <v>2018</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+    <row r="43" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C42" s="9">
-        <v>2018</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="C43" s="9">
         <v>2018</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C44" s="9">
         <v>2018</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="9">
+        <v>2018</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C45" s="9">
-        <v>2017</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C46" s="9">
-        <v>2016</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>25</v>
+        <v>2017</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C47" s="9">
         <v>2016</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="9">
+        <v>2016</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+    <row r="49" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B49" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="C48" s="9">
-        <v>2015</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C49" s="9">
         <v>2015</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="9">
+        <v>2015</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C50" s="9">
-        <v>2013</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="9">
+        <v>2013</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="9">
-        <v>2012</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="90" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>91</v>
@@ -1980,21 +1978,38 @@
         <v>2012</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>86</v>
       </c>
     </row>
+    <row r="53" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C53" s="9">
+        <v>2012</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A11:G52">
-    <sortCondition descending="1" ref="C11:C52"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:G53">
+    <sortCondition descending="1" ref="C12:C53"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="E9" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{C16A25D3-9458-409D-AB93-CF367A4FD2FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACCD7CF-CE02-42C1-8926-279B0E75D139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E437F82B-D86C-4849-B3B5-9F3C52AAE7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
@@ -571,9 +571,6 @@
     <t>Roundtables at official pre-summit event ahead of the India AI Impact Summit 2026, IIIT-H, organized by SFLC.in, VISWAM.AI, FOSS United, and The Linux Foundation</t>
   </si>
   <si>
-    <t>images/sflc-roundtable-jan26.jpeg</t>
-  </si>
-  <si>
     <t>AI4Bharat: Transforming the Landscape of Indian Language Technology</t>
   </si>
   <si>
@@ -581,6 +578,9 @@
   </si>
   <si>
     <t>publications/presentations/eai4bharat_bits_course_2026.pdf</t>
+  </si>
+  <si>
+    <t>/images/sflc-roundtable-jan26.jpeg</t>
   </si>
 </sst>
 </file>
@@ -650,7 +650,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -701,6 +701,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1064,9 @@
   <cols>
     <col min="1" max="2" width="29.26953125" style="1"/>
     <col min="3" max="3" width="29.26953125" style="9"/>
-    <col min="4" max="16384" width="29.26953125" style="1"/>
+    <col min="4" max="4" width="29.26953125" style="1"/>
+    <col min="5" max="5" width="29.26953125" style="4"/>
+    <col min="6" max="16384" width="29.26953125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.35">
@@ -1095,9 +1103,9 @@
         <v>2026</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="E2" s="12"/>
       <c r="F2" s="17" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>142</v>
@@ -1105,17 +1113,17 @@
     </row>
     <row r="3" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="C3" s="9">
         <v>2026</v>
       </c>
       <c r="D3" s="16"/>
-      <c r="E3" s="1" t="s">
-        <v>164</v>
+      <c r="E3" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="1" t="s">
@@ -1135,7 +1143,7 @@
       <c r="D4" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>155</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -1156,7 +1164,7 @@
         <v>2025</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F5" s="2"/>
@@ -1191,7 +1199,7 @@
       <c r="C7" s="9">
         <v>2025</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="4" t="s">
         <v>134</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1211,7 +1219,7 @@
       <c r="D8" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="4" t="s">
         <v>131</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -1232,7 +1240,7 @@
         <v>2025</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F9" s="2"/>
@@ -1251,7 +1259,7 @@
         <v>2025</v>
       </c>
       <c r="D10" s="13"/>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="18" t="s">
         <v>138</v>
       </c>
       <c r="F10" s="14" t="s">
@@ -1271,7 +1279,7 @@
       <c r="C11" s="9">
         <v>2025</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="4" t="s">
         <v>128</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1289,7 +1297,7 @@
         <v>2025</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="4" t="s">
         <v>120</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -1306,7 +1314,7 @@
       <c r="C13" s="9">
         <v>2025</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1340,7 +1348,7 @@
       <c r="C15" s="9">
         <v>2024</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1357,7 +1365,7 @@
       <c r="C16" s="9">
         <v>2024</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="4" t="s">
         <v>67</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -1391,7 +1399,7 @@
       <c r="C18" s="9">
         <v>2023</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1408,7 +1416,7 @@
       <c r="C19" s="10">
         <v>2022</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="19" t="s">
         <v>141</v>
       </c>
       <c r="G19" s="7" t="s">
@@ -1467,7 +1475,7 @@
       <c r="C23" s="11">
         <v>2022</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1487,7 +1495,7 @@
       <c r="D24" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -1521,7 +1529,7 @@
       <c r="C26" s="9">
         <v>2021</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="4" t="s">
         <v>48</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -1538,7 +1546,7 @@
       <c r="C27" s="9">
         <v>2021</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -1555,7 +1563,7 @@
       <c r="C28" s="9">
         <v>2021</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="4" t="s">
         <v>50</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -1572,7 +1580,7 @@
       <c r="C29" s="11">
         <v>2021</v>
       </c>
-      <c r="E29" s="7"/>
+      <c r="E29" s="19"/>
       <c r="G29" s="1" t="s">
         <v>112</v>
       </c>
@@ -1587,7 +1595,7 @@
       <c r="C30" s="9">
         <v>2021</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -1604,7 +1612,7 @@
       <c r="C31" s="9">
         <v>2021</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -1649,7 +1657,7 @@
       <c r="C34" s="11">
         <v>2020</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G34" s="1" t="s">
@@ -1669,7 +1677,7 @@
       <c r="D35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="4" t="s">
         <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -1689,7 +1697,7 @@
       <c r="C36" s="11">
         <v>2020</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="4" t="s">
         <v>54</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -1726,7 +1734,7 @@
       <c r="C38" s="11">
         <v>2020</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="4" t="s">
         <v>53</v>
       </c>
       <c r="F38" s="1" t="s">
@@ -1746,7 +1754,7 @@
       <c r="C39" s="11">
         <v>2019</v>
       </c>
-      <c r="E39" s="7"/>
+      <c r="E39" s="19"/>
       <c r="G39" s="1" t="s">
         <v>85</v>
       </c>
@@ -1761,7 +1769,7 @@
       <c r="C40" s="11">
         <v>2019</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="4" t="s">
         <v>59</v>
       </c>
       <c r="F40" s="1" t="s">
@@ -1781,7 +1789,7 @@
       <c r="C41" s="9">
         <v>2018</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G41" s="1" t="s">
@@ -1812,7 +1820,7 @@
       <c r="C43" s="9">
         <v>2018</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="4" t="s">
         <v>69</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -1829,7 +1837,7 @@
       <c r="C44" s="9">
         <v>2018</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -1846,7 +1854,7 @@
       <c r="C45" s="9">
         <v>2018</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="4" t="s">
         <v>71</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -1866,7 +1874,7 @@
       <c r="C46" s="9">
         <v>2017</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G46" s="1" t="s">
@@ -1903,7 +1911,7 @@
       <c r="D48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -1920,7 +1928,7 @@
       <c r="C49" s="9">
         <v>2015</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="4" t="s">
         <v>74</v>
       </c>
       <c r="G49" s="1" t="s">
@@ -1940,7 +1948,7 @@
       <c r="D50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G50" s="1" t="s">
@@ -1960,7 +1968,7 @@
       <c r="D51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G51" s="1" t="s">
@@ -1977,7 +1985,7 @@
       <c r="C52" s="9">
         <v>2012</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="4" t="s">
         <v>77</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -1994,7 +2002,7 @@
       <c r="C53" s="9">
         <v>2012</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="4" t="s">
         <v>123</v>
       </c>
       <c r="F53" s="1" t="s">

--- a/scripts/my_talks.xlsx
+++ b/scripts/my_talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankunchu.FAREAST\Documents\src\anoopkunchukuttan.github.io\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E437F82B-D86C-4849-B3B5-9F3C52AAE7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750C4FDF-CFFF-4200-AD38-D992B78D2CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9F223068-8B85-418E-B88F-438BCC691FB8}"/>
   </bookViews>
@@ -565,9 +565,6 @@
     <t>Prof. Pushpak Bhattacharya: The Guru and the Visionary Paving the Way for Indic NLP</t>
   </si>
   <si>
-    <t>U4nderstanding Trust and Safety in AI: From Code to Creativity</t>
-  </si>
-  <si>
     <t>Roundtables at official pre-summit event ahead of the India AI Impact Summit 2026, IIIT-H, organized by SFLC.in, VISWAM.AI, FOSS United, and The Linux Foundation</t>
   </si>
   <si>
@@ -581,6 +578,9 @@
   </si>
   <si>
     <t>/images/sflc-roundtable-jan26.jpeg</t>
+  </si>
+  <si>
+    <t>Understanding Trust and Safety in AI: From Code to Creativity</t>
   </si>
 </sst>
 </file>
@@ -1094,10 +1094,10 @@
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="C2" s="9">
         <v>2026</v>
@@ -1105,7 +1105,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="12"/>
       <c r="F2" s="17" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>142</v>
@@ -1113,17 +1113,17 @@
     </row>
     <row r="3" spans="1:7" s="3" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="C3" s="9">
         <v>2026</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="1" t="s">
